--- a/excel_files/excel_image_embedded_output.xlsx
+++ b/excel_files/excel_image_embedded_output.xlsx
@@ -166,6 +166,631 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -468,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,12 +1151,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -558,12 +1183,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -590,12 +1215,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -622,17 +1247,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.arco.gr/wp-content/uploads/2023/02/Belden-9504-Multi-Conductor-Cable.jpg</t>
+          <t>https://gudangkabel.com/93-large_default/belden-9504-kabel-data-ftp-.jpg</t>
         </is>
       </c>
     </row>
@@ -654,12 +1279,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -686,17 +1311,3234 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>https://www.sakthiavtronics.in/wp-content/uploads/2022/04/BOSCH-LBB-1990-Plena-Voice-Alarm-Controller-2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="180" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A0222-RF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1U+1U Enclosure for 2"D Floor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://resource.fs.com/mall/products/800x800/145167.B.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="180" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A0422-RF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1U+1U Enclosure for 4"D Floor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26298.jpg?v=1718067947</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A0622-RF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2U+2U Enclosure for 6"D Floor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.alldataresource.com/assets/images_chatsworth/CMS-chatsworth-media-assets-catalog-productimages-raised-floor-enclosures-for-patch-panels-series_zone_raisdflr_encl.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A0822-RF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4U+4U Enclosure for 8"D Floor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://buy.wesco.com/medias/sys_master/300WX300H/300WX300H/9127602880542.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A1411-RF-HR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7U Enclosure for 14"D Floor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>288.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.alldataresource.com/assets/images_chatsworth/CMS-chatsworth-media-assets-catalog-productimages-raised-floor-enclosure-for-active-components-series_zone_ceiling_a1411-rf-hr.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A0802-RF-DI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4U+4U Enclosure for 9"D Floor</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26303.jpg?v=1718067943</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="180" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A1422-RF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11U Enclosure for 14"D Floor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>416.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26301.jpg?v=1718067943</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A1222-LP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2’ X 2’ Ceiling Enclosure</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.alldataresource.com/assets/images_chatsworth/CMS-chatsworth-media-assets-catalog-productimages-ceiling-enclosure-for-wiring-blocks-series_zone_ceiling_a1222-lp.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="180" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A1024-LP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2’ X 4’ Ceiling Enclosure</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26312.jpg?v=1718067934</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="180" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A1222-PP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2’ X 2’ Ceiling Enclosure</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://cdn.pimber.ly/public/asset/raw/663b2857ae13c25e14022b2b/08892e13/66e34a92ce135c00125fd99d/A1222-PP_13812-002_1520x1020.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A1024-PP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2’ X 4’ Ceiling Enclosure</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://cdn.pimber.ly/public/asset/raw/663b2857ae13c25e14022b2b/5f3bad9d/66e34a754a5acc0012b31cad/A1024-PP_1520x1020.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A1222-HR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2’ X 2’ Ceiling Enclosure</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://az343058.vo.msecnd.net/productlargeimages/277955bf02244f0cb0d85c2ca5ea55f8.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A1024-HR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2’ X 4’ Ceiling Enclosure</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>http://www.alldataresource.com/assets/images/PR0560V6.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="180" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BCE-24-P</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1U, Plenum Enclosure</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://resource.fs.com/images/3910904529879876.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BCE-24-N</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1U, Non-Plenum Enclosure</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://impacttechnicalproducts.com/wp-content/uploads/CMS-chatsworth-media-assets-catalog-productimages-basic-consolidation-enclosure-for-a-single-patch-panel-19-x-1u-bce-24-n_cmyk300.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BCE-48-P</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2U, Plenum Enclosure</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.alldataresource.com/cdn-cgi/image/width=500,height=400,quality=100/assets/images_chatsworth/CMS-chatsworth-media-assets-catalog-productimages-basic-consolidation-enclosure-for-a-single-patch-panel-19-x-2u-bce-48_cmyk300.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BCE-48-N</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2U, Non-Plenum Enclosure</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.alldataresource.com/cdn-cgi/image/width=500,height=400,quality=100/assets/images_chatsworth/CMS-chatsworth-media-assets-catalog-productimages-basic-consolidation-enclosure-for-a-single-patch-panel-19-x-2u-bce-48_cmyk300.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="180" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BCE-6-P</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Plenum Enclosure</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://ibetww.com/wp-content/uploads/2023/09/plenum-hvac-ducting.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="180" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AAT-AWM-H</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Active Wall-Mount Enclosure</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://images.eanixter.com/viewex/PR28402V6.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="180" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10557-001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3/8” Threaded Rod</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://i.ebayimg.com/images/g/UdkAAOSws-9ec2-M/s-l1600.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11440-001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>I-Beam Clamp</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://buy.wesco.com/medias/sys_master/300WX300H/300WX300H/h71/h17/9700195500062.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>10697-001</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3/8-16 UNC-2A Threaded Rod. 6’L</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.zoro.com/static/cms/product/email/Wirexpress+Div+of+Anixter+Inc_PR25715V0.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>04002-002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3/8” Threaded Rod Coupling Kit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.zoro.com/static/cms/product/email/Wirexpress+Div+of+Anixter+Inc_PR25715V0.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20141-090</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3/8” Washer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>416.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.sturdybuiltonline.com/cdn-cgi/image/quality=85/assets/images/bolts/trailer+stainless+steel+flat+washer+38+inch+-+m+-+24448.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="180" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20142-091</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3/8-16 Hex Nut</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://nikatto.com/3183-large_default/3-8-16-hex-nut-grade-5-unc-black.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="180" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>40605-001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Equipment Mounting Screws, #12-24, 50 pk</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://llcinconline.com/wp-content/uploads/2023/03/40605-001-768x1024.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="180" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>02006-201</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Saf-T-Grip® Cable Management Straps, 25 pk</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/11331.jpg?v=1718074778</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="180" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHROME LOCK KIT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lock Kit</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>http://twacomm.com/cdn/shop/files/26430.jpg?v=1718067897</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="180" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SPARE KEYS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Spare Key</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://img.freepik.com/premium-photo/padlock-isolated-transparent-white-background-isolated-white-background-no-shadow-text-logo-job-id-0e16b7fd1cc14869ac3329da039150a5_890746-139079.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="180" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FP-B33-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Foam Kit for A0622 and A0822</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26431_3f7aa095-588e-4d18-a362-dfdaac42e479.jpg?v=1718067896</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="180" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FP-B33-11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Foam Kit for A1422</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26431.jpg?v=1718067893</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="180" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FP-B33-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Foam Kit for Ceiling Enclosure (2 required)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://twacomm.com/cdn/shop/files/26431.jpg?v=1718067893</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RF-BRACKET</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Raised Floor Mounting Brackets, 4 each</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://az343058.vo.msecnd.net/productlargeimages/6405fcd095fd41d784925f3a53b4ac3f.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HME-38X24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 4U</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://2665680.fs1.hubspotusercontent-na1.net/hubfs/2665680/Case+Studies/Chatsworth+Products/Chatsworth-Products_10.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="180" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HME-38X30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 4U</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://broadwayfurnituregroup.com/wp-content/uploads/2024/07/HHC-03.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HME-38X36</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 4U</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://2665680.fs1.hubspotusercontent-na1.net/hubfs/2665680/Case+Studies/Chatsworth+Products/Chatsworth-Products_10.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="180" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HME-38X42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 4U</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://i.ebayimg.com/images/g/ZGMAAOSwk0Rkkee8/s-l1200.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="180" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HME-38X48</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 8U</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://i.ebayimg.com/images/g/ZGMAAOSwk0Rkkee8/s-l1200.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HME-54X24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 6U</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://cdn11.bigcommerce.com/s-bmqf4dxrop/images/stencil/1280x1280/products/31177/49984/12419-748-Front-Done__40622.1736535233.jpg?c=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="180" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HME-54X30</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 6U</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://i.ebayimg.com/images/g/B5MAAOxyJs5RZGjp/s-l1200.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="180" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HME-54X36</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 6U</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>416.0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://thumbs.dreamstime.com/b/corn-tin-can-product-isolated-white-transparent-background-300900878.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HME-54X42</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 6U</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://cdn11.bigcommerce.com/s-bmqf4dxrop/images/stencil/1280x1280/products/31177/49984/12419-748-Front-Done__40622.1736535233.jpg?c=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="180" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HME-54X48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ethospace Furniture, 12U</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://i.ebayimg.com/images/g/ZGMAAOSwk0Rkkee8/s-l1200.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WA064-CAP</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wireless Access Enclosure</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.zoro.com/static/cms/product/full/Wirexpress+Div+of+Anixter+Inc_PR5478V2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WA064-WAP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Wireless Access Enclosure</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AAT-ACE-DOME</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Wireless Ceiling Enclosure with 6" Dome</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AAT-CAP</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>14.5"W x 12.1"L x 5"H, Shallow Enclosure, White</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AAT-CAP-S</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>14.5"W x 12.1"L x 5"H, Shallow Enclosure, White</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AAT-CAP-00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Blank Faceplate, White</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AAT-CAP-35</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Faceplate for Cisco® Aironet™ 350, White</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AAT-CAP-11</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Faceplate for Cisco® Aironet™ 1100, White</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AAT-CAP-12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Faceplate for Cisco® Aironet™ 1200, White</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AAT-CAP-00-KIT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10" Enclosure w/Cisco® 00 Faceplate, White</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AAT-CAP-35-KIT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10" Enclosure w/Cisco® 35 Faceplate, White</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AAT-CAP-11-KIT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>10" Enclosure w/Cisco® 1100 Faceplate, White</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AAT-CAP-12-KIT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10" Enclosure w/Cisco® 1200 Faceplate, White</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WA061-WAP</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>11"W x 8"L x 3"D, Enclosure, White</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>416.0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AAT-MWME-P</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>16"W x 12"L x 5"H, Mini Enclosure, Gray</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AAT-WMEGG-P</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Chatsworth Products</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>14"W x 16"L x 6"H, Enclosure w/Flexiglass Door</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CS55</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Quick fit ceiling speaker.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CS75</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Quick fit 2-way ceiling speaker.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CS85</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Quick fit 2-way ceiling speaker.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AGRO5.4</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Set composed of four CS55 dual cone 4 ¼” in-ceiling loudspeakers and a COM3 amplifier, suited for versatile 100 Volt background music and announcement systems, covering around 60 m².</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AGRO7.10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Set composed of ten CS75 two-way 5 ¼” in-ceiling loudspeakers and a COM12 amplifier, suited for high-quality 100 Volt background music and announcement systems, covering around 120 m².</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AGRO8.16</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Set composed of sixteen CS85 two-way 8” in-ceiling loudspeakers and a COM24 amplifier, suited for highly demanding 100 Volt background music and announcement systems, covering around 200 m².</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CELO2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2” High-end slim ceiling speaker with an ultra-compact size for smooth integration into any interior and clear, crisp sound.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CELO5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5” High-end slim ceiling speaker with an uncompromised design, producing stunningly detailed and clear sound.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CELO6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>6” High-end slim ceiling speaker, providing the perfect harmony and balance of sound for a large number of applications.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CELO8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>8” High-end slim ceiling speaker, the most powerful of its kind, reaching lower frequencies for high-fidelity sound with powerful and detailing low frequencies.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SENSO2.2</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Set composed of two CELO2 speakers and an AMP20 mini stereo amplifier, offering a compact high-end in-ceiling audio solution with extraordinary sound, covering around 30 m² with background music.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SENSO2.4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Set composed of four CELO2 speakers and an AMP20 mini stereo amplifier, offering a compact high-end in-ceiling audio solution with extraordinary sound, covering around 60 m² with background music.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SENSO5.4</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Set composed of four CELO5 loudspeakers and a DPA152 Class-D amplifier, aesthetically blending into any environment while guaranteeing an unsurpassed sound experience, covering around 60 m² with warm and true-to-nature sound.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SENSO6.8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Set composed of eight CELO6 loudspeakers and a DPA154 Class-D amplifier, aesthetically blending into any environment while guaranteeing an unsurpassed sound experience, covering around 120 m² with high-fidelity sound.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MERO2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2” High-end slim in-wall speaker with an ultra-compact size for smooth integration into any interior.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MERO5</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5” High-end slim in-wall speaker consisting of a 5” aluminum cone woofer and a complementary 1” dome tweeter.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MERO6</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>6” High-end slim in-wall speaker consisting of a 6” aluminum cone woofer and a complementary 1” dome tweeter.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CERRA6.2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Set composed of two MERO6 loudspeakers and a DPA152 Class-D amplifier, aesthetically blending into any environment while guaranteeing an unsurpassed sound experience, covering around 30 m² with high-fidelity sound.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KYDO</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Design column speaker constructed using 6 x 2” broadband loudspeakers, providing extraordinary sound quality for small to medium coverage distances (up to 8 meters).</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AXIR</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Design column speaker constructed using 12 x 2” broadband loudspeakers, providing extraordinary sound quality for medium to large coverage distances (up to 16 meters).</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GIAX</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Design column speaker constructed using 24 x 2” broadband loudspeakers, providing extraordinary sound quality for very large coverage distances (up to 32 meters).</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BASO10</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>10” Compact bass reflex cabinet with a 10” high-performance woofer and RMS power rating of 225 Watt.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BASO12</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>12” Compact bass reflex cabinet with a 12” high-performance woofer and RMS power rating of 500 Watt.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BASO15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>15” Compact bass reflex cabinet with a 15” high-performance woofer and RMS power rating of 700 Watt.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CONGRESS2.3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Set featuring two AXIR design column speakers and a BASO10 bass cabinet, powered by a SMQ350 WaveDynamics™ Class-D amplifier, ideal for intelligible speech and music over medium distances, covering around 60 m².</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CONGRESS3.3</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Set featuring two GIAX design column speakers and two BASO12 bass cabinets, powered by a SMQ500 WaveDynamics™ Class-D amplifier, ideal for intelligible speech and music over large distances, covering around 120 m².</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ATEO4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4” 2-Way Wall speaker with CleverMount™ bracket, ensuring true-to-nature, high-fidelity reproduction of music and speech.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ATEO6</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>6” 2-Way Wall speaker with CleverMount™ bracket, ensuring true-to-nature, high-fidelity reproduction of music and speech.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ATEO2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2” Wall speaker with CleverMount™ bracket, guaranteeing a clear and crisp sound with minimal visual impact.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FESTA4.4</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Set composed of four ATEO4 loudspeakers and a DPA152 Class-D amplifier, guaranteeing high-quality sound with elegant aesthetics for any environment, covering around 60 m² with true-to-nature high-fidelity music and speech.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FESTA4.3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Set composed of two ATEO4 loudspeakers and a BASO10 bass cabinet, powered by a DPA153 Class-D amplifier, guaranteeing impressive sound with elegant aesthetics for any environment, covering around 30 m² with true-to-nature high-fidelity music and speech.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FESTA4.5</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Set composed of four ATEO4 loudspeakers and a BASO10 bass cabinet, powered by a DPA153 Class-D amplifier, guaranteeing impressive sound with elegant aesthetics for any environment, covering around 60 m² with true-to-nature high-fidelity music and speech.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FESTA6.3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Set composed of two ATEO6 loudspeakers and a BASO10 bass cabinet, powered by a SMQ350 WaveDynamics™ Class-D amplifier, guaranteeing impressive sound with elegant aesthetics for any environment, covering around 60 m² with a warm and powerful sound.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FESTA6.4</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Set composed of four ATEO6 loudspeakers and a DPA252 Class-D amplifier, guaranteeing high-quality sound with elegant aesthetics for any environment, covering around 60 m² with a warm and powerful sound.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>416.0</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FESTA6.5</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Set composed of four ATEO6 loudspeakers and a BASO12 bass cabinet, powered by a SMQ350 WaveDynamics™ Class-D amplifier, guaranteeing impressive sound with elegant aesthetics for any environment, covering around 120 m² with a warm and powerful sound.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>XENO6</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>6” Full range loudspeaker cabinet - 2-way, featuring a 1” dome tweeter and a 6” Mid / Low frequency driver, ensuring a high-fidelity sound.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>XENO8</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>8” Full range loudspeaker cabinet - 2-way, featuring a 1” dome tweeter and an 8” Mid / Low frequency driver, ensuring a true-to-nature, high-fidelity reproduction of music and speech.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>VEXO8</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>8” High power loudspeaker cabinet - 2-way, providing a powerful and detailed sound in a compact cabinet.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FESTA8.2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Set composed of two XENO8 loudspeakers and a SMA350 WaveDynamics™ Class-D power amplifier, suitable for fixed installations requiring high-quality and full-range sound without an additional bass cabinet, covering around 30 m².</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FESTA8.4</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Set composed of four XENO8 loudspeakers and a SMA350 WaveDynamics™ Class-D power amplifier, suitable for fixed installations requiring high-quality and full-range sound without an additional bass cabinet, covering around 60 m².</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FORTE8.3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Set composed of two VEXO8 loudspeakers and a BASO15 bass cabinet, powered by a SMQ500 WaveDynamics™ Class-D amplifier, suitable for fixed and mobile applications requiring a powerful solution with a small footprint, covering around 60 m² with stunning sound.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>864.0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FORTE8.6</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Set composed of four VEXO8 loudspeakers and two BASO15 bass cabinets, powered by a SMQ750 WaveDynamics™ Class-D amplifier, suitable for fixed and mobile applications requiring a powerful solution with a small footprint, covering around 120 m² with stunning sound.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PX112 MK2</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>12” Loudspeaker cabinet 2-way, featuring a 12” high output woofer and a compression driver with 1.3” voice coil.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>680.0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PX110 MK2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10” Loudspeaker cabinet 2-way, featuring a 10” high output woofer and a compression driver with 1” voice coil.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FORTE10.6</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Set composed of four PX110MK2 cabinets and two BASO15 bass cabinets, powered by a SMQ750 WaveDynamics™ Class-D amplifier, suitable for medium to large scale installations requiring high power sound, covering around 160 m² with very clear sound and powerful bass.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FORTE12.6</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Set composed of four PX112MK2 cabinets and two BASO15 bass cabinets, powered by a SMQ750 WaveDynamics™ Class-D amplifier, suited for large scale installations with highly demanding performance criteria, covering around 200 m² with extremely powerful sound.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>WX302/O</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3” Outdoor wall speaker 2-way, specifically designed for outdoor use, ensuring true-to-nature, high-fidelity reproduction of music and speech.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>WX502/O</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5” Outdoor wall speaker 2-way, a powerful performance speaker especially designed for outdoor use, ensuring true-to-nature, high fidelity reproduction of music and speech.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>WX802/O</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>8” Outdoor wall speaker 2-way, a powerful loudspeaker cabinet specifically designed for outdoor use, ensuring clear and powerful sound reproduction.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SSP500</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2-way flush mount sauna speaker, especially designed to be used in rooms with very high temperature and humidity.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PURRA5.1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Set composed of two SSP500 loudspeakers in combination with an AMP20 mini stereo amplifier, providing high-quality sound for areas with high temperature and humidity.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>416.0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PURRA5.2</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Set composed of two WX502/O loudspeakers and a DPA152 Class-D amplifier, offering a weather and humidity resistant solution with extraordinary sound for outdoor and humid areas, covering around 30 m².</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>37.0</t>
         </is>
       </c>
     </row>
